--- a/assets/data/excel/professions.xlsx
+++ b/assets/data/excel/professions.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>{"hp": 1.5, "atk": 0.8, "def": 1.4, "spd": 0.9}</t>
+          <t>{"hp":1.3,"atk":0.8,"spd":0.9}</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>{"hp": 0.9, "atk": 1.5, "def": 0.8, "spd": 1.3}</t>
+          <t>{"hp":0.8,"atk":1.3,"spd":1.1}</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>{"hp": 1.1, "atk": 0.7, "def": 1.0, "spd": 1.2}</t>
+          <t>{"hp":1.0,"atk":0.7,"spd":1.2}</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
